--- a/artfynd/A 9224-2022 artfynd.xlsx
+++ b/artfynd/A 9224-2022 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122323953</v>
+        <v>122323886</v>
       </c>
       <c r="B2" t="n">
-        <v>57390</v>
+        <v>56587</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,20 +687,20 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100049</v>
+        <v>102613</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Orre</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Lyrurus tetrix</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -708,10 +708,14 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I2" t="inlineStr"/>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
@@ -720,10 +724,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>442624</v>
+        <v>442620</v>
       </c>
       <c r="R2" t="n">
-        <v>6383293</v>
+        <v>6383296</v>
       </c>
       <c r="S2" t="n">
         <v>20</v>
@@ -755,7 +759,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>14:04</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -765,12 +769,12 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>14:04</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>Flyger ivrigt ljudande kring hygget</t>
+          <t>Hörs väster vägen/hygget, utifrån Trollamossen-hållet</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -797,10 +801,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122323886</v>
+        <v>122323953</v>
       </c>
       <c r="B3" t="n">
-        <v>56587</v>
+        <v>57390</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -809,20 +813,20 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>102613</v>
+        <v>100049</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Orre</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lyrurus tetrix</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -830,14 +834,10 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="I3" t="inlineStr"/>
       <c r="M3" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -846,10 +846,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>442620</v>
+        <v>442624</v>
       </c>
       <c r="R3" t="n">
-        <v>6383296</v>
+        <v>6383293</v>
       </c>
       <c r="S3" t="n">
         <v>20</v>
@@ -881,7 +881,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>14:04</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -891,12 +891,12 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>14:04</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>Hörs väster vägen/hygget, utifrån Trollamossen-hållet</t>
+          <t>Flyger ivrigt ljudande kring hygget</t>
         </is>
       </c>
       <c r="AD3" t="b">

--- a/artfynd/A 9224-2022 artfynd.xlsx
+++ b/artfynd/A 9224-2022 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122323886</v>
+        <v>122323953</v>
       </c>
       <c r="B2" t="n">
-        <v>56587</v>
+        <v>57390</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,20 +687,20 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>102613</v>
+        <v>100049</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Orre</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lyrurus tetrix</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -708,14 +708,10 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="I2" t="inlineStr"/>
       <c r="M2" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
@@ -724,10 +720,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>442620</v>
+        <v>442624</v>
       </c>
       <c r="R2" t="n">
-        <v>6383296</v>
+        <v>6383293</v>
       </c>
       <c r="S2" t="n">
         <v>20</v>
@@ -759,7 +755,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>14:04</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -769,12 +765,12 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>14:04</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>Hörs väster vägen/hygget, utifrån Trollamossen-hållet</t>
+          <t>Flyger ivrigt ljudande kring hygget</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -801,10 +797,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122323953</v>
+        <v>122323886</v>
       </c>
       <c r="B3" t="n">
-        <v>57390</v>
+        <v>56587</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -813,20 +809,20 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100049</v>
+        <v>102613</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Orre</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Lyrurus tetrix</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -834,10 +830,14 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I3" t="inlineStr"/>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -846,10 +846,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>442624</v>
+        <v>442620</v>
       </c>
       <c r="R3" t="n">
-        <v>6383293</v>
+        <v>6383296</v>
       </c>
       <c r="S3" t="n">
         <v>20</v>
@@ -881,7 +881,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>14:04</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -891,12 +891,12 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>14:04</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>Flyger ivrigt ljudande kring hygget</t>
+          <t>Hörs väster vägen/hygget, utifrån Trollamossen-hållet</t>
         </is>
       </c>
       <c r="AD3" t="b">

--- a/artfynd/A 9224-2022 artfynd.xlsx
+++ b/artfynd/A 9224-2022 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>122323886</v>
       </c>
       <c r="B2" t="n">
-        <v>56587</v>
+        <v>56592</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -804,7 +804,7 @@
         <v>122323953</v>
       </c>
       <c r="B3" t="n">
-        <v>57390</v>
+        <v>57395</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>

--- a/artfynd/A 9224-2022 artfynd.xlsx
+++ b/artfynd/A 9224-2022 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122323886</v>
+        <v>122323953</v>
       </c>
       <c r="B2" t="n">
-        <v>56592</v>
+        <v>57395</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,20 +687,15 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>102613</v>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>Orre</t>
-        </is>
+        <v>100049</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lyrurus tetrix</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -708,14 +703,10 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="I2" t="inlineStr"/>
       <c r="M2" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
@@ -724,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>442620</v>
+        <v>442624</v>
       </c>
       <c r="R2" t="n">
-        <v>6383296</v>
+        <v>6383293</v>
       </c>
       <c r="S2" t="n">
         <v>20</v>
@@ -759,7 +750,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>14:04</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -769,12 +760,12 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>14:04</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>Hörs väster vägen/hygget, utifrån Trollamossen-hållet</t>
+          <t>Flyger ivrigt ljudande kring hygget</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -801,10 +792,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122323953</v>
+        <v>122323886</v>
       </c>
       <c r="B3" t="n">
-        <v>57395</v>
+        <v>56592</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -813,20 +804,15 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100049</v>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>Spillkråka</t>
-        </is>
+        <v>102613</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Lyrurus tetrix</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -834,10 +820,14 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I3" t="inlineStr"/>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -846,10 +836,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>442624</v>
+        <v>442620</v>
       </c>
       <c r="R3" t="n">
-        <v>6383293</v>
+        <v>6383296</v>
       </c>
       <c r="S3" t="n">
         <v>20</v>
@@ -881,7 +871,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>14:04</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -891,12 +881,12 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>14:04</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>Flyger ivrigt ljudande kring hygget</t>
+          <t>Hörs väster vägen/hygget, utifrån Trollamossen-hållet</t>
         </is>
       </c>
       <c r="AD3" t="b">

--- a/artfynd/A 9224-2022 artfynd.xlsx
+++ b/artfynd/A 9224-2022 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>122323953</v>
       </c>
       <c r="B2" t="n">
-        <v>57395</v>
+        <v>57399</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -692,6 +692,11 @@
       </c>
       <c r="E2" t="n">
         <v>100049</v>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -795,7 +800,7 @@
         <v>122323886</v>
       </c>
       <c r="B3" t="n">
-        <v>56592</v>
+        <v>56596</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -809,6 +814,11 @@
       </c>
       <c r="E3" t="n">
         <v>102613</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Orre</t>
+        </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>

--- a/artfynd/A 9224-2022 artfynd.xlsx
+++ b/artfynd/A 9224-2022 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122323953</v>
+        <v>122323886</v>
       </c>
       <c r="B2" t="n">
-        <v>57399</v>
+        <v>56596</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,20 +687,20 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100049</v>
+        <v>102613</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Orre</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Lyrurus tetrix</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -708,10 +708,14 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I2" t="inlineStr"/>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
@@ -720,10 +724,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>442624</v>
+        <v>442620</v>
       </c>
       <c r="R2" t="n">
-        <v>6383293</v>
+        <v>6383296</v>
       </c>
       <c r="S2" t="n">
         <v>20</v>
@@ -755,7 +759,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>14:04</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -765,12 +769,12 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>14:04</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>Flyger ivrigt ljudande kring hygget</t>
+          <t>Hörs väster vägen/hygget, utifrån Trollamossen-hållet</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -797,10 +801,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122323886</v>
+        <v>122323953</v>
       </c>
       <c r="B3" t="n">
-        <v>56596</v>
+        <v>57399</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -809,20 +813,20 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>102613</v>
+        <v>100049</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Orre</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lyrurus tetrix</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -830,14 +834,10 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="I3" t="inlineStr"/>
       <c r="M3" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -846,10 +846,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>442620</v>
+        <v>442624</v>
       </c>
       <c r="R3" t="n">
-        <v>6383296</v>
+        <v>6383293</v>
       </c>
       <c r="S3" t="n">
         <v>20</v>
@@ -881,7 +881,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>14:04</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -891,12 +891,12 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>14:04</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>Hörs väster vägen/hygget, utifrån Trollamossen-hållet</t>
+          <t>Flyger ivrigt ljudande kring hygget</t>
         </is>
       </c>
       <c r="AD3" t="b">

--- a/artfynd/A 9224-2022 artfynd.xlsx
+++ b/artfynd/A 9224-2022 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122323886</v>
+        <v>122323953</v>
       </c>
       <c r="B2" t="n">
-        <v>56596</v>
+        <v>57399</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,20 +687,20 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>102613</v>
+        <v>100049</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Orre</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lyrurus tetrix</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -708,14 +708,10 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="I2" t="inlineStr"/>
       <c r="M2" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
@@ -724,10 +720,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>442620</v>
+        <v>442624</v>
       </c>
       <c r="R2" t="n">
-        <v>6383296</v>
+        <v>6383293</v>
       </c>
       <c r="S2" t="n">
         <v>20</v>
@@ -759,7 +755,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>14:04</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -769,12 +765,12 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>14:04</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>Hörs väster vägen/hygget, utifrån Trollamossen-hållet</t>
+          <t>Flyger ivrigt ljudande kring hygget</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -801,10 +797,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122323953</v>
+        <v>122323886</v>
       </c>
       <c r="B3" t="n">
-        <v>57399</v>
+        <v>56596</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -813,20 +809,20 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100049</v>
+        <v>102613</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Orre</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Lyrurus tetrix</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -834,10 +830,14 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I3" t="inlineStr"/>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -846,10 +846,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>442624</v>
+        <v>442620</v>
       </c>
       <c r="R3" t="n">
-        <v>6383293</v>
+        <v>6383296</v>
       </c>
       <c r="S3" t="n">
         <v>20</v>
@@ -881,7 +881,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>14:04</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -891,12 +891,12 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>14:04</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>Flyger ivrigt ljudande kring hygget</t>
+          <t>Hörs väster vägen/hygget, utifrån Trollamossen-hållet</t>
         </is>
       </c>
       <c r="AD3" t="b">

--- a/artfynd/A 9224-2022 artfynd.xlsx
+++ b/artfynd/A 9224-2022 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>122323886</v>
       </c>
       <c r="B2" t="n">
-        <v>56596</v>
+        <v>56597</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -804,7 +804,7 @@
         <v>122323953</v>
       </c>
       <c r="B3" t="n">
-        <v>57399</v>
+        <v>57400</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>

--- a/artfynd/A 9224-2022 artfynd.xlsx
+++ b/artfynd/A 9224-2022 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122323886</v>
+        <v>122323953</v>
       </c>
       <c r="B2" t="n">
-        <v>56597</v>
+        <v>57400</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,20 +687,20 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>102613</v>
+        <v>100049</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Orre</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lyrurus tetrix</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -708,14 +708,10 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="I2" t="inlineStr"/>
       <c r="M2" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
@@ -724,10 +720,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>442620</v>
+        <v>442624</v>
       </c>
       <c r="R2" t="n">
-        <v>6383296</v>
+        <v>6383293</v>
       </c>
       <c r="S2" t="n">
         <v>20</v>
@@ -759,7 +755,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>14:04</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -769,12 +765,12 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>14:04</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>Hörs väster vägen/hygget, utifrån Trollamossen-hållet</t>
+          <t>Flyger ivrigt ljudande kring hygget</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -801,10 +797,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122323953</v>
+        <v>122323886</v>
       </c>
       <c r="B3" t="n">
-        <v>57400</v>
+        <v>56597</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -813,20 +809,20 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100049</v>
+        <v>102613</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Orre</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Lyrurus tetrix</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -834,10 +830,14 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I3" t="inlineStr"/>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -846,10 +846,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>442624</v>
+        <v>442620</v>
       </c>
       <c r="R3" t="n">
-        <v>6383293</v>
+        <v>6383296</v>
       </c>
       <c r="S3" t="n">
         <v>20</v>
@@ -881,7 +881,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>14:04</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -891,12 +891,12 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>14:04</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>Flyger ivrigt ljudande kring hygget</t>
+          <t>Hörs väster vägen/hygget, utifrån Trollamossen-hållet</t>
         </is>
       </c>
       <c r="AD3" t="b">

--- a/artfynd/A 9224-2022 artfynd.xlsx
+++ b/artfynd/A 9224-2022 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122323953</v>
+        <v>122323886</v>
       </c>
       <c r="B2" t="n">
-        <v>57400</v>
+        <v>56597</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,20 +687,20 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100049</v>
+        <v>102613</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Orre</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Lyrurus tetrix</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -708,10 +708,14 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I2" t="inlineStr"/>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
@@ -720,10 +724,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>442624</v>
+        <v>442620</v>
       </c>
       <c r="R2" t="n">
-        <v>6383293</v>
+        <v>6383296</v>
       </c>
       <c r="S2" t="n">
         <v>20</v>
@@ -755,7 +759,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>14:04</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -765,12 +769,12 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>14:04</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>Flyger ivrigt ljudande kring hygget</t>
+          <t>Hörs väster vägen/hygget, utifrån Trollamossen-hållet</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -797,10 +801,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122323886</v>
+        <v>122323953</v>
       </c>
       <c r="B3" t="n">
-        <v>56597</v>
+        <v>57400</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -809,20 +813,20 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>102613</v>
+        <v>100049</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Orre</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lyrurus tetrix</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -830,14 +834,10 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="I3" t="inlineStr"/>
       <c r="M3" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -846,10 +846,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>442620</v>
+        <v>442624</v>
       </c>
       <c r="R3" t="n">
-        <v>6383296</v>
+        <v>6383293</v>
       </c>
       <c r="S3" t="n">
         <v>20</v>
@@ -881,7 +881,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>14:04</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -891,12 +891,12 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>14:04</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>Hörs väster vägen/hygget, utifrån Trollamossen-hållet</t>
+          <t>Flyger ivrigt ljudande kring hygget</t>
         </is>
       </c>
       <c r="AD3" t="b">
